--- a/Exp4_OpenStack/eda/results/compute/cost/tables/cost.xlsx
+++ b/Exp4_OpenStack/eda/results/compute/cost/tables/cost.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="compute_by_iteration" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cumulative_cost" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="k_step_multiplier" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing_integrity" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3122,7 +3123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3301,7 +3302,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3310,7 +3311,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>12</v>
@@ -3322,45 +3323,177 @@
         <v>10</v>
       </c>
       <c r="H3" t="n">
+        <v>12.13246680743164</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12.00843142198192</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.213246680743164</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.065677308970028</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>10.94275411301189</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.1240353854497274</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.08783682048215087</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.9019397527886904</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0102234267291587</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
         <v>15.9812487757206</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I4" t="n">
         <v>15.88579708344407</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>1.59812487757206</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>1.111393650902642</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>14.77440343254142</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N4" t="n">
         <v>0.09545169227653079</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O4" t="n">
         <v>0.06954360491472478</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0.9244836645673983</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R4" t="n">
         <v>0.005972730517876996</v>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="n">
+        <v>21.58704584598541</v>
+      </c>
+      <c r="I5" t="n">
+        <v>21.46979348070092</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.158704584598541</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.064023269083765</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20.40577021161715</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1172523652844959</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.04928989712974753</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.9452784951310073</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.005431607739245226</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3375,7 +3508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3448,7 +3581,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3466,34 +3599,34 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5341309774584241</v>
+        <v>0.8637964290380478</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05816491842269898</v>
+        <v>0.09107694248358408</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4759660590357251</v>
+        <v>0.7727194865544637</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3511,16 +3644,16 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7642756702502569</v>
+        <v>1.042719006737073</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1066698820061154</v>
+        <v>0.113029234011968</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6576057882441415</v>
+        <v>0.9296897727251053</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -3538,7 +3671,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3556,16 +3689,16 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8881627671586143</v>
+        <v>1.019290898442268</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1215367031759686</v>
+        <v>0.09339888314406077</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7666260639826457</v>
+        <v>0.9258920152982076</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -3583,7 +3716,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3601,16 +3734,16 @@
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9004443417655097</v>
+        <v>1.208808493349287</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1304764927095837</v>
+        <v>0.1184615831242667</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.769967849055926</v>
+        <v>1.090346910225021</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3628,7 +3761,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3646,16 +3779,16 @@
         <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9195627234379451</v>
+        <v>1.236774473587672</v>
       </c>
       <c r="G6" t="n">
-        <v>0.131597854230139</v>
+        <v>0.09535132507483164</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7879648692078061</v>
+        <v>1.14142314851284</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3673,7 +3806,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3691,16 +3824,16 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8266064300802018</v>
+        <v>1.292655619515313</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1132037894593345</v>
+        <v>0.08590041167206235</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7134026406208674</v>
+        <v>1.206755207843251</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -3718,7 +3851,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3736,16 +3869,16 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9168503722879622</v>
+        <v>1.340774379968643</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1160068799389733</v>
+        <v>0.084584817621443</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8008434923489889</v>
+        <v>1.2561895623472</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3763,7 +3896,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3781,16 +3914,16 @@
         <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7977522869242563</v>
+        <v>1.391426257226202</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09374246795972188</v>
+        <v>0.08993552446365356</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7040098189645343</v>
+        <v>1.301490732762549</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -3808,7 +3941,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3826,16 +3959,16 @@
         <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>0.812432265414132</v>
+        <v>1.217528891828325</v>
       </c>
       <c r="G10" t="n">
-        <v>0.09124689565764534</v>
+        <v>0.1565379636155234</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7211853697564867</v>
+        <v>1.060990928212802</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3853,7 +3986,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRPO_LA0</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3871,19 +4004,19 @@
         <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8557766903109021</v>
+        <v>1.518692357738813</v>
       </c>
       <c r="G11" t="n">
-        <v>0.09050306770536634</v>
+        <v>0.1374006237586339</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6776500529050827</v>
+        <v>1.257256348530452</v>
       </c>
       <c r="J11" t="n">
-        <v>0.08762356970045301</v>
+        <v>0.1240353854497274</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -3898,7 +4031,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3907,7 +4040,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -3916,16 +4049,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.174772451387511</v>
+        <v>0.5341309774584241</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07764317704571617</v>
+        <v>0.05816491842269898</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1.097129274341795</v>
+        <v>0.4759660590357251</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -3943,7 +4076,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3952,7 +4085,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -3961,16 +4094,16 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>1.337008321086566</v>
+        <v>0.7642756702502569</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1097030517127779</v>
+        <v>0.1066698820061154</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1.227305269373788</v>
+        <v>0.6576057882441415</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -3988,7 +4121,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3997,7 +4130,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -4006,16 +4139,16 @@
         <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>1.634791824883885</v>
+        <v>0.8881627671586143</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1217930142747031</v>
+        <v>0.1215367031759686</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.512998810609182</v>
+        <v>0.7666260639826457</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -4033,7 +4166,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4042,7 +4175,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -4051,16 +4184,16 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>1.705454114807977</v>
+        <v>0.9004443417655097</v>
       </c>
       <c r="G15" t="n">
-        <v>0.127253956662284</v>
+        <v>0.1304764927095837</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1.578200158145693</v>
+        <v>0.769967849055926</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -4078,7 +4211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4087,7 +4220,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -4096,16 +4229,16 @@
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>1.636446531878577</v>
+        <v>0.9195627234379451</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1135137485795551</v>
+        <v>0.131597854230139</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1.522932783299022</v>
+        <v>0.7879648692078061</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -4123,7 +4256,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4132,7 +4265,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
@@ -4141,16 +4274,16 @@
         <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>1.702453856269519</v>
+        <v>0.8266064300802018</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1165949348608653</v>
+        <v>0.1132037894593345</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1.585858921408653</v>
+        <v>0.7134026406208674</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -4168,7 +4301,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4177,7 +4310,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>7</v>
@@ -4186,16 +4319,16 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>1.581697883208593</v>
+        <v>0.9168503722879622</v>
       </c>
       <c r="G18" t="n">
-        <v>0.108406510286861</v>
+        <v>0.1160068799389733</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1.473291372921732</v>
+        <v>0.8008434923489889</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -4213,7 +4346,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4222,7 +4355,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -4231,16 +4364,16 @@
         <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>1.683850161963039</v>
+        <v>0.7977522869242563</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1165024271938536</v>
+        <v>0.09374246795972188</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1.567347734769185</v>
+        <v>0.7040098189645343</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -4258,7 +4391,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4267,7 +4400,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
@@ -4276,16 +4409,16 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>1.64012582037184</v>
+        <v>0.812432265414132</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1092284525103039</v>
+        <v>0.09124689565764534</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1.530897367861536</v>
+        <v>0.7211853697564867</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -4303,7 +4436,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4312,7 +4445,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -4321,27 +4454,927 @@
         <v>9</v>
       </c>
       <c r="F21" t="n">
+        <v>0.8557766903109021</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.09050306770536634</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6776500529050827</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.08762356970045301</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.740790468851725</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.09232272538873884</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.648467743462986</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.911218772663011</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1140012128485574</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.797217559814453</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.913638647397359</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1256611853837967</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.787977462013562</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.91981811967161</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.105501925945282</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.814316193726328</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.488427925109863</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1123429236147139</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.37608500149515</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.321622651351823</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.09609270360734727</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.225529947744476</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.387109926276737</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1233621253569921</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.263747800919745</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.369854836000337</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.08946264902750652</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.28039218697283</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>9</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.245588750243187</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1012386082278358</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.144350142015351</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.288975748419761</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.1040372096829944</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.067686173452271</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.1172523652844959</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.174772451387511</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.07764317704571617</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.097129274341795</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.337008321086566</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.1097030517127779</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.227305269373788</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.634791824883885</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.1217930142747031</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.512998810609182</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.705454114807977</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.127253956662284</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.578200158145693</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.636446531878577</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.1135137485795551</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.522932783299022</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>6</v>
+      </c>
+      <c r="E37" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.702453856269519</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.1165949348608653</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.585858921408653</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" t="n">
+        <v>6</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.581697883208593</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.108406510286861</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.473291372921732</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>8</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.683850161963039</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.1165024271938536</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.567347734769185</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E40" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.64012582037184</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.1092284525103039</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.530897367861536</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9</v>
+      </c>
+      <c r="F41" t="n">
         <v>1.884647809863091</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G41" t="n">
         <v>0.1107543777757221</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
         <v>1.678441739810838</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J41" t="n">
         <v>0.09545169227653079</v>
       </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="b">
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4356,7 +5389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4696,7 +5729,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4705,7 +5738,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -4723,7 +5756,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4732,25 +5765,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.174772451387511</v>
+        <v>0.8637964290380478</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4759,25 +5792,25 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.511780772474077</v>
+        <v>1.906515435775121</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4786,25 +5819,25 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.146572597357962</v>
+        <v>2.925806334217389</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4813,25 +5846,25 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>5.852026712165939</v>
+        <v>4.134614827566677</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4840,25 +5873,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>7.488473244044516</v>
+        <v>5.371389301154348</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4867,25 +5900,25 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>9.190927100314035</v>
+        <v>6.664044920669661</v>
       </c>
       <c r="F19" t="n">
         <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4894,25 +5927,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>10.77262498352263</v>
+        <v>8.004819300638305</v>
       </c>
       <c r="F20" t="n">
         <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4921,25 +5954,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>12.45647514548567</v>
+        <v>9.396245557864507</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4948,25 +5981,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>14.0966009658575</v>
+        <v>10.61377444969283</v>
       </c>
       <c r="F22" t="n">
         <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GRPO_LA5</t>
+          <t>GRPO_LA0_ThL1B</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4975,18 +6008,612 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>15.88579708344406</v>
+        <v>12.00843142198192</v>
       </c>
       <c r="F23" t="n">
         <v>10</v>
       </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.174772451387511</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.511780772474077</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4.146572597357962</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5.852026712165939</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7.488473244044516</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9.190927100314035</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10.77262498352263</v>
+      </c>
+      <c r="F31" t="n">
+        <v>7</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>12.45647514548567</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>9</v>
+      </c>
+      <c r="E33" t="n">
+        <v>14.0966009658575</v>
+      </c>
+      <c r="F33" t="n">
+        <v>9</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="n">
+        <v>15.88579708344406</v>
+      </c>
+      <c r="F34" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.740790468851725</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.652009241514736</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="n">
+        <v>5.565647888912095</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7.485466008583705</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>9.973893933693567</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" t="n">
+        <v>12.29551658504539</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" t="n">
+        <v>14.68262651132213</v>
+      </c>
+      <c r="F42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" t="n">
+        <v>17.05248134732246</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>19.29807009756565</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="n">
+        <v>21.46979348070091</v>
+      </c>
+      <c r="F45" t="n">
+        <v>10</v>
+      </c>
+      <c r="G45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5001,7 +6628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5240,6 +6867,278 @@
         <v>10</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>method=GRPO, ThL1B</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TOTAL (production)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.227151682707998</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.208656066689227</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.799823198559536</v>
+      </c>
+      <c r="I7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>method=GRPO, ThL1B</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0943751041094462</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1047695678141382</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.110139891264518</v>
+      </c>
+      <c r="I8" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>method=GRPO, ThL1B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>build (PTO only)</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>method=GRPO, ThL1B</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>train</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.11588502936893</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.106018157733811</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.887307475506534</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>method=GRPO, ThL1B</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>eval-gen</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>arm</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>iteration</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>n_sessions</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>n_sessions_production</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>gpu_hours</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8637964290380478</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>RESUMED (cumulative log is the correct number)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
